--- a/MVP_Effort_Estimation_Aurion_v5.xlsx
+++ b/MVP_Effort_Estimation_Aurion_v5.xlsx
@@ -64,7 +64,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -106,11 +106,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -138,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,12 +181,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6808,78 +6797,78 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Phase 2 — TLS + DNS + WAF + SHA-pin</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>🔵 In Progress</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>Code shipped (commit 352cc56). Route53 zone created. BLOCKED on Cloudflare DNS choice (A/B/C).</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Fully applied 2026-05-22 (115 resources). api-dev.aurionclinical.com live, ACM cert valid, WAF in front, ALB returning HTTPS. ECS service waiting on first image push.</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Phase 3 — GitHub Actions CI/CD with OIDC</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>🟢 Done</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>🟡 Verify</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Workflows + IAM OIDC trust shipped (commit 2a0fd11). Awaits secrets after P2 apply.</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Workflows + IAM OIDC trust shipped (commit 2a0fd11). Roles exist in AWS. 4 GitHub Secrets need wiring: AWS_ACCOUNT_ID, AWS_DEPLOY_ROLE_DEV, AWS_DEPLOY_ROLE_PROD, ECR_REGISTRY.</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>P1, P2</t>
         </is>
       </c>
     </row>
@@ -7108,76 +7097,76 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>EXT-02</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Cloudflare DNS delegation decision</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>🔴 Blocker</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Cloudflare DNS delegation (subdomain to AWS)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>Three paths on the table (manual records / subdomain delegation / Cloudflare TF provider). Recommend subdomain delegation.</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Option B chosen + applied 2026-05-22. 4 NS records at Cloudflare for api-dev.aurionclinical.com delegate to AWS. Propagation verified via dig.</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>EXT-03</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>First Phase 2 full apply against dev</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>🟠 Not Started</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>~15-20 min compute + ~5 min cert validation post-DNS delegation.</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Applied 2026-05-22. 115 resources created. ALB returns 503 (no image yet — expected). TLS valid.</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>EXT-02</t>
         </is>

--- a/MVP_Effort_Estimation_Aurion_v5.xlsx
+++ b/MVP_Effort_Estimation_Aurion_v5.xlsx
@@ -716,34 +716,34 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIF('Mobile'!C5:C41,"*Done*")</f>
+        <f>COUNTIF('Mobile'!C5:C43,"*Done*")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIF('Mobile'!C5:C41,"*Verify*")</f>
+        <f>COUNTIF('Mobile'!C5:C43,"*Verify*")</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIF('Mobile'!C5:C41,"*Not Started*")</f>
+        <f>COUNTIF('Mobile'!C5:C43,"*Not Started*")</f>
         <v/>
       </c>
       <c r="F16" s="7">
-        <f>COUNTIF('Mobile'!C5:C41,"*Blocker*")</f>
+        <f>COUNTIF('Mobile'!C5:C43,"*Blocker*")</f>
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>COUNTIF('Mobile'!C5:C41,"*Future*")</f>
+        <f>COUNTIF('Mobile'!C5:C43,"*Future*")</f>
         <v/>
       </c>
       <c r="H16" s="7">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'Mobile'!C5:C41))))*(NOT(ISNUMBER(SEARCH("Future",'Mobile'!C5:C41))))*'Mobile'!E5:E41)</f>
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'Mobile'!C5:C43))))*(NOT(ISNUMBER(SEARCH("Future",'Mobile'!C5:C43))))*'Mobile'!E5:E43)</f>
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'Mobile'!C5:C41))))*(NOT(ISNUMBER(SEARCH("Future",'Mobile'!C5:C41))))*'Mobile'!F5:F41)</f>
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'Mobile'!C5:C43))))*(NOT(ISNUMBER(SEARCH("Future",'Mobile'!C5:C43))))*'Mobile'!F5:F43)</f>
         <v/>
       </c>
     </row>
@@ -906,34 +906,34 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="7">
-        <f>COUNTIF('External'!C5:C12,"*Done*")</f>
+        <f>COUNTIF('External'!C5:C15,"*Done*")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>COUNTIF('External'!C5:C12,"*Verify*")</f>
+        <f>COUNTIF('External'!C5:C15,"*Verify*")</f>
         <v/>
       </c>
       <c r="E21" s="7">
-        <f>COUNTIF('External'!C5:C12,"*Not Started*")</f>
+        <f>COUNTIF('External'!C5:C15,"*Not Started*")</f>
         <v/>
       </c>
       <c r="F21" s="7">
-        <f>COUNTIF('External'!C5:C12,"*Blocker*")</f>
+        <f>COUNTIF('External'!C5:C15,"*Blocker*")</f>
         <v/>
       </c>
       <c r="G21" s="7">
-        <f>COUNTIF('External'!C5:C12,"*Future*")</f>
+        <f>COUNTIF('External'!C5:C15,"*Future*")</f>
         <v/>
       </c>
       <c r="H21" s="7">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'External'!C5:C12))))*(NOT(ISNUMBER(SEARCH("Future",'External'!C5:C12))))*'External'!E5:E12)</f>
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'External'!C5:C15))))*(NOT(ISNUMBER(SEARCH("Future",'External'!C5:C15))))*'External'!E5:E15)</f>
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'External'!C5:C12))))*(NOT(ISNUMBER(SEARCH("Future",'External'!C5:C12))))*'External'!F5:F12)</f>
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done",'External'!C5:C15))))*(NOT(ISNUMBER(SEARCH("Future",'External'!C5:C15))))*'External'!F5:F15)</f>
         <v/>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2633,108 +2633,184 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>COGNITO-IOS</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Cognito hosted UI login + MFA challenge + Keychain token mgmt</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>CognitoAuth.swift wraps ASWebAuthenticationSession + PKCE + /oauth2/token exchange. LoginView reduced from email/password form to single 'Sign in' button. Cognito drives password + TOTP MFA on its surface. Tokens persist to Keychain; APIClient sends id_token as Bearer (commit 6cb033b).</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>Cognito User Pool (Done)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>CONFIG-URL</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Config.swift Release URL → https://api-dev.aurionclinical.com</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>iOS Release builds point at the dev backend for the pilot (commit 3cbcbfa).</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>P2 apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>M018</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>MediaPipe face detection (backup)</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>🟣 Future</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E42" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F40" s="15" t="n">
+      <c r="F42" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>Pilot follow-up — revisit only if clinical safety committee asks.</t>
         </is>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H42" s="14" t="inlineStr">
         <is>
           <t>M015 Apple Vision</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>M019</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Ray-Ban Meta SDK</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>🟣 Future</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="E43" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="F41" s="15" t="n">
+      <c r="F43" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Deferred post-pilot — pilot ships iPhone/iPad fallback.</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>Partner SDK access</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="E43" s="3">
-        <f>SUM(E5:E41)</f>
+      <c r="E45" s="3">
+        <f>SUM(E5:E43)</f>
         <v/>
       </c>
-      <c r="F43" s="3">
-        <f>SUM(F5:F41)</f>
+      <c r="F45" s="3">
+        <f>SUM(F5:F43)</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="16" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>REMAINING (not 🟢 Done, excl. 🟣 Future)</t>
         </is>
       </c>
-      <c r="E44" s="3">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C41)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C41)))) * E5:E41)</f>
+      <c r="E46" s="3">
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C43)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C43)))) * E5:E43)</f>
         <v/>
       </c>
-      <c r="F44" s="3">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C41)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C41)))) * F5:F41)</f>
+      <c r="F46" s="3">
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C43)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C43)))) * F5:F43)</f>
         <v/>
       </c>
     </row>
@@ -3962,7 +4038,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Auth (api/v1/auth.py)</t>
+          <t>Auth (api/v1/auth.py + /auth/me)</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -3983,7 +4059,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Cognito JWKS + JWT + dev seed (now @dataclass per Q-06).</t>
+          <t>Cognito JWKS + JWT + dev seed (Q-06 dataclass). /auth/me added (commit 6cb033b) — validates Bearer JWT, auto-provisions UserModel on first Cognito sign-in.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -6835,76 +6911,76 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Phase 3 — GitHub Actions CI/CD with OIDC</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>🟡 Verify</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Workflows + IAM OIDC trust shipped (commit 2a0fd11). Roles exist in AWS. 4 GitHub Secrets need wiring: AWS_ACCOUNT_ID, AWS_DEPLOY_ROLE_DEV, AWS_DEPLOY_ROLE_PROD, ECR_REGISTRY.</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>All 4 GitHub Secrets wired + end-to-end CI run green 2026-05-22. Hardened bundle (paths filter, layer cache, plan-before-apply, drop :latest) merged via commit c8eb144.</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>P1, P2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Phase 4 — Cognito MFA + SNS + alarms + CloudTrail + Flow Logs + KMS rotation</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>🟠 Not Started</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Phase 4 — MFA + SNS + alarms + CloudTrail + Flow Logs + audit bucket</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>Includes 5 missing operational alarms, SNS topic, GuardDuty enable.</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Cognito MFA ON (TOTP) + Cognito hosted UI domain + OAuth code flow + 5 new operational alarms + SNS topic (confirmed) + CloudTrail multi-region + VPC Flow Logs + S3 access logs on PHI buckets (commits 857c8de + 2aa95c7).</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -6989,7 +7065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7239,7 +7315,7 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>~5 min per physician via Cognito hosted UI.</t>
+          <t>~5 min per physician via Cognito hosted UI. User pool MFA is ON, 3 pilot accounts pre-provisioned (perry, marie, faical.sawadogo) — they enroll TOTP on first sign-in.</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -7362,33 +7438,147 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>EXT-09</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Pilot Cognito user provisioning (admin-create + groups)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>scripts/provision_pilot_users.sh run 2026-05-23. 3 users in FORCE_CHANGE_PASSWORD state across CLINICIAN + ADMIN groups.</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>EXT-03</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>EXT-10</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>SNS alarm subscription confirmed</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>faical.sawadogo@aurionclinical.com confirmed 2026-05-23. CloudWatch alarms now route to a real mailbox.</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>EXT-11</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>AI provider keys populated in Secrets Manager</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>OpenAI / Anthropic / Google AI / AssemblyAI uploaded 2026-05-22, ECS service rolled.</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="E14" s="3">
-        <f>SUM(E5:E12)</f>
+      <c r="E17" s="3">
+        <f>SUM(E5:E15)</f>
         <v/>
       </c>
-      <c r="F14" s="3">
-        <f>SUM(F5:F12)</f>
+      <c r="F17" s="3">
+        <f>SUM(F5:F15)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>REMAINING (not 🟢 Done, excl. 🟣 Future)</t>
         </is>
       </c>
-      <c r="E15" s="3">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C12)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C12)))) * E5:E12)</f>
+      <c r="E18" s="3">
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C15)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C15)))) * E5:E15)</f>
         <v/>
       </c>
-      <c r="F15" s="3">
-        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C12)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C12)))) * F5:F12)</f>
+      <c r="F18" s="3">
+        <f>SUMPRODUCT((NOT(ISNUMBER(SEARCH("Done", C5:C15)))) * (NOT(ISNUMBER(SEARCH("Future", C5:C15)))) * F5:F15)</f>
         <v/>
       </c>
     </row>

--- a/MVP_Effort_Estimation_Aurion_v5.xlsx
+++ b/MVP_Effort_Estimation_Aurion_v5.xlsx
@@ -6987,38 +6987,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>Phase 5 — Runbooks + IAM Identity Center + backup-restore drill</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>🟠 Not Started</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Phase 5 — Operational runbooks</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>🟢 Done</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>Mostly markdown + 1 IAM rework. Pre-pilot human-gated.</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>5 runbooks shipped: incident response, DSAR, backup-restore drill SOP, Cognito user mgmt, pilot launch checklist (commit 8d40c3e). IAM Identity Center migration is a separate post-pilot follow-up (tracked as AUR-OPS-IIC).</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
